--- a/community_mapping_photo_list.xlsx
+++ b/community_mapping_photo_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AY CM code\anyang-community-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E79D64B-EF08-4F5B-A3DB-B3D5886B0B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360729E8-0D19-43D4-B76A-57C9E2ED9EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31005" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="커뮤니티매핑_사진목록" sheetId="1" r:id="rId1"/>
@@ -1974,15 +1974,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I230"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
     <col min="3" max="3" width="15.5546875" customWidth="1"/>
     <col min="8" max="8" width="22.33203125" customWidth="1"/>
     <col min="9" max="9" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -6529,7 +6529,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -6819,7 +6819,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -7138,7 +7138,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -7921,7 +7921,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -8037,7 +8037,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -8182,7 +8182,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -8356,7 +8356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -8501,7 +8501,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -8588,7 +8588,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -8617,7 +8617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -8658,29 +8658,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>522</v>
       </c>
